--- a/data/trans_orig/KIDM_C_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_1_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>26189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34533</t>
+          <t>34825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63669</t>
+          <t>64052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13825</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>24219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31471</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47781</t>
+          <t>49488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58654</t>
+          <t>58501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60224</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66830</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>64862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70171</t>
+          <t>70219</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127730</t>
+          <t>128422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136195</t>
+          <t>136215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54955</t>
+          <t>54790</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88977</t>
+          <t>88756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95703</t>
+          <t>95680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29367</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29871</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35533</t>
+          <t>35521</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63814</t>
+          <t>63862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>32011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>188670</t>
+          <t>188910</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201518</t>
+          <t>201568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>248497</t>
+          <t>249248</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>261087</t>
+          <t>261299</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>442702</t>
+          <t>442118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>460603</t>
+          <t>459717</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
